--- a/data/trans_orig/IP08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122266</t>
+          <t>123291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133579</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127761</t>
+          <t>128932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>141006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255349</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271634</t>
+          <t>271838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22814</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21005</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36350</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>55073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172349</t>
+          <t>172585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184517</t>
+          <t>184419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175792</t>
+          <t>174910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191137</t>
+          <t>191736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352625</t>
+          <t>352232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372674</t>
+          <t>372175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125195</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133600</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127179</t>
+          <t>126816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139407</t>
+          <t>139209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255622</t>
+          <t>256753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270403</t>
+          <t>270647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56357</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177169</t>
+          <t>176642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193117</t>
+          <t>193263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177043</t>
+          <t>176324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191444</t>
+          <t>191638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360087</t>
+          <t>360549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380710</t>
+          <t>381893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>45465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123077</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160145</t>
+          <t>159801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611876</t>
+          <t>612448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636661</t>
+          <t>635556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>624037</t>
+          <t>623482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>652292</t>
+          <t>652450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1242881</t>
+          <t>1243225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1279949</t>
+          <t>1282043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>43222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118217</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130828</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129033</t>
+          <t>127706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>142752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251690</t>
+          <t>250819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270760</t>
+          <t>270228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20775</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40150</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48385</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170159</t>
+          <t>170793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185583</t>
+          <t>185283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183685</t>
+          <t>183241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200214</t>
+          <t>200491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358998</t>
+          <t>358980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381808</t>
+          <t>382559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>18944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128821</t>
+          <t>127982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141706</t>
+          <t>141324</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133105</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147678</t>
+          <t>147648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265967</t>
+          <t>266152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285891</t>
+          <t>285629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60599</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178701</t>
+          <t>178988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194991</t>
+          <t>194904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170834</t>
+          <t>171719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188173</t>
+          <t>188526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357363</t>
+          <t>356226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379435</t>
+          <t>379229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97881</t>
+          <t>97242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>87486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118812</t>
+          <t>116351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164766</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612776</t>
+          <t>613415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>639941</t>
+          <t>641064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634695</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665818</t>
+          <t>666021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1256728</t>
+          <t>1258420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299398</t>
+          <t>1299717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119444</t>
+          <t>118711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>129533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131279</t>
+          <t>130435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140892</t>
+          <t>140382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253918</t>
+          <t>253513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267567</t>
+          <t>267754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179869</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192883</t>
+          <t>192659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195705</t>
+          <t>195614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210481</t>
+          <t>210542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380027</t>
+          <t>380067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399643</t>
+          <t>399580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139973</t>
+          <t>140462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149458</t>
+          <t>149592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150490</t>
+          <t>151411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160543</t>
+          <t>160365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295067</t>
+          <t>295246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308155</t>
+          <t>308010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189660</t>
+          <t>190336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200649</t>
+          <t>200593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186971</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198082</t>
+          <t>197907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380660</t>
+          <t>380633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396277</t>
+          <t>396473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643595</t>
+          <t>642674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665079</t>
+          <t>664994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>678064</t>
+          <t>679218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>700524</t>
+          <t>701318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329847</t>
+          <t>1328135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1361228</t>
+          <t>1360756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51701</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67544</t>
+          <t>72286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99041</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109793</t>
+          <t>110361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88711</t>
+          <t>86260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128490</t>
+          <t>128727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190149</t>
+          <t>185407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234646</t>
+          <t>235010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>40380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>66977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>150132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177116</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218239</t>
+          <t>216903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234515</t>
+          <t>234138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375108</t>
+          <t>376583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406832</t>
+          <t>407945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>32675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>167181</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180894</t>
+          <t>182074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154061</t>
+          <t>152611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171722</t>
+          <t>171128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326803</t>
+          <t>325949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349593</t>
+          <t>349533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55449</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145031</t>
+          <t>144705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158172</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142799</t>
+          <t>143211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161138</t>
+          <t>161078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293752</t>
+          <t>292805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315490</t>
+          <t>315364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>49148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>82883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131983</t>
+          <t>133640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138048</t>
+          <t>137584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>208543</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581036</t>
+          <t>582013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615215</t>
+          <t>615748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628001</t>
+          <t>626344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679338</t>
+          <t>679480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1216338</t>
+          <t>1224099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1286833</t>
+          <t>1287297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11582</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25144</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5539</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15259</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17537</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12071</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24145</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>135540</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>127933</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>141495</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128961</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>123291</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>133187</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>123467</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>133587</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135540</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>128932</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>141006</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>255338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271838</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20887</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37304</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15696</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10744</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22578</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21744</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>20406</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35130</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55073</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>183783</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>174838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>191255</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>179467</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>172585</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184419</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>173419</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184559</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183783</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>174910</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>191736</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352232</t>
+          <t>353356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372175</t>
+          <t>372879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22148</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4225</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12895</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12754</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10448</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22841</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30721</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>134291</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127509</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139712</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>129948</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>124922</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>133592</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>125063</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133696</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>134291</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126816</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139209</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256753</t>
+          <t>255780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270647</t>
+          <t>271119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15658</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30325</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16052</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32673</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15749</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31523</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15491</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30805</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55895</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>184914</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176804</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191471</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>186402</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>176642</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>193263</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>177792</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>193566</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>184914</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>176324</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>191638</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360549</t>
+          <t>359754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381893</t>
+          <t>380845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70691</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97757</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45465</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68573</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45625</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>69264</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>69555</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>98523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120983</t>
+          <t>122977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>158856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>638527</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>624248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>651314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>935</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>624778</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>612448</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>635556</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>611757</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>635396</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>638527</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>623482</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>652450</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1243225</t>
+          <t>1244170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1282043</t>
+          <t>1280049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11963</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25755</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8981</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20819</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21771</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11932</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26978</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43222</t>
+          <t>41823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>128929</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142721</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>125292</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118538</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>130376</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>117586</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130520</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,91%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136657</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>127706</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>142752</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250819</t>
+          <t>252218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270228</t>
+          <t>270332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22669</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40727</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21075</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35565</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20965</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36054</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23344</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40594</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>48022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>71746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192413</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>183108</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>201166</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>178552</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170793</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>170304</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>185393</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>192413</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>183241</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>200491</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358980</t>
+          <t>358447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>382559</t>
+          <t>382171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18678</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33352</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19870</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14052</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27394</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14077</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27522</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18944</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33478</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55816</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141299</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133240</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>147914</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>135506</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127982</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141324</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>127854</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141299</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141299</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>133114</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>147648</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266152</t>
+          <t>266942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285629</t>
+          <t>286250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20227</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36410</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14662</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30578</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14228</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28551</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19870</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>36677</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61736</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180719</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>171986</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>188169</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188438</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>178988</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>194904</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>181015</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>195338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>180719</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171719</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>188526</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356226</t>
+          <t>357271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379229</t>
+          <t>379251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209566</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209566</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209566</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85622</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>117859</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69593</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>97242</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>70360</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96227</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>87486</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>116351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164447</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205744</t>
+          <t>207696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>651088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>635648</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>667885</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>627788</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613415</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641064</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>614430</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>640297</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>651088</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>637156</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>666021</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258420</t>
+          <t>1256468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299717</t>
+          <t>1298358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15637</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14996</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13943</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136225</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>130297</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>140605</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>125538</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118711</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>129533</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>119764</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>129270</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136225</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>130435</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140382</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253513</t>
+          <t>254026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267754</t>
+          <t>267492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145934</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145934</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145934</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145934</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145934</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13770</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27943</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14111</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27721</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14210</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26645</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13817</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28745</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>204318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196416</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210589</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187174</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>179049</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192659</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>180125</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>192560</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>204318</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>195614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210542</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380067</t>
+          <t>380165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399580</t>
+          <t>399879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206770</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206770</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206770</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15438</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9532</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14770</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15403</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14332</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156675</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150305</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160474</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>145700</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140462</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149592</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>139829</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149729</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,86%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156675</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>151411</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160365</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295246</t>
+          <t>295804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308010</t>
+          <t>308561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165743</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165743</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165743</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155232</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155232</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155232</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165743</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165743</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19276</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5926</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16183</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17341</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7829</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19742</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>193107</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186460</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>197738</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>196169</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190336</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>200593</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>189178</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>200607</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>193107</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>185994</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>197907</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380633</t>
+          <t>380784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396473</t>
+          <t>395643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63119</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37234</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>59554</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36956</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>59632</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40454</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62554</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115865</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690325</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>678653</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>700425</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>654581</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642674</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>664994</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>642596</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>665272</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>690325</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>679218</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>701318</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328135</t>
+          <t>1327536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1360756</t>
+          <t>1359340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10454</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47236</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18314</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72286</t>
+          <t>58983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105273</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78670</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>115452</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>105274</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98966</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>110361</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,76%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>116481</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86260</t>
+          <t>102600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128727</t>
+          <t>113378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>221756</t>
+          <t>213833</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185407</t>
+          <t>187994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235010</t>
+          <t>224978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16817</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33485</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13345</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40380</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66977</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>201517</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>218185</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>169152</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150132</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>177167</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>227113</t>
+          <t>168267</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216903</t>
+          <t>161282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234138</t>
+          <t>174210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>396265</t>
+          <t>379961</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376583</t>
+          <t>368339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407945</t>
+          <t>388550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235002</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235002</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235002</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253048</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253048</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253048</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>443560</t>
+          <t>419415</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443560</t>
+          <t>419415</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>443560</t>
+          <t>419415</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12933</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30662</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21961</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148483</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137679</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155408</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>174632</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167181</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>182074</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164326</t>
+          <t>141060</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152611</t>
+          <t>133964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171128</t>
+          <t>146300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>338959</t>
+          <t>289544</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325949</t>
+          <t>278216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349533</t>
+          <t>298724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189142</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189142</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189142</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374428</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374428</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374428</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17921</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10582</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23257</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56396</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>144303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135880</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>151455</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>152289</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>144705</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157380</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>153034</t>
+          <t>151479</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143211</t>
+          <t>143713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>156734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>305324</t>
+          <t>295782</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292805</t>
+          <t>285016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315364</t>
+          <t>304257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>71419</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>114800</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49148</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82883</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137584</t>
+          <t>125646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200782</t>
+          <t>178982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>609754</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583825</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>627206</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>852</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>601348</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>582013</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>615748</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>660955</t>
+          <t>569366</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>626344</t>
+          <t>556487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679480</t>
+          <t>580507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1262303</t>
+          <t>1179120</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1224099</t>
+          <t>1148091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1287297</t>
+          <t>1201427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
